--- a/benchmark/data/optimization.xlsx
+++ b/benchmark/data/optimization.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\merag\Git\BioRedis_engine\benchmark\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07FF7C2-BFA0-4D26-8839-819236DFB819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650DF9F5-4325-4FF0-8A27-B0029B6F85D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="47">
   <si>
     <t>CodonTransformer</t>
   </si>
@@ -159,10 +159,13 @@
     <t>id</t>
   </si>
   <si>
-    <t>BioRedis-engine</t>
-  </si>
-  <si>
     <t>https://github.com/jkubis96/BioRedis_engine</t>
+  </si>
+  <si>
+    <t>BIOREDIS-engine</t>
+  </si>
+  <si>
+    <t>https://github.com/jkubis96/BIOREDIS_engine</t>
   </si>
 </sst>
 </file>
@@ -625,10 +628,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -660,10 +663,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>

--- a/benchmark/data/optimization.xlsx
+++ b/benchmark/data/optimization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\merag\Git\BioRedis_engine\benchmark\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650DF9F5-4325-4FF0-8A27-B0029B6F85D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251C5AAB-87C7-4F5C-9CEB-C372B215DB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
   <si>
     <t>CodonTransformer</t>
   </si>
@@ -159,13 +159,10 @@
     <t>id</t>
   </si>
   <si>
-    <t>https://github.com/jkubis96/BioRedis_engine</t>
-  </si>
-  <si>
-    <t>BIOREDIS-engine</t>
-  </si>
-  <si>
     <t>https://github.com/jkubis96/BIOREDIS_engine</t>
+  </si>
+  <si>
+    <t>BIOREDIS</t>
   </si>
 </sst>
 </file>
@@ -631,7 +628,7 @@
         <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -666,7 +663,7 @@
         <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
